--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Adjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>29.69</v>
+        <v>28.17</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>433</v>
+        <v>401</v>
       </c>
       <c r="D2">
-        <v>24.78</v>
+        <v>24.25</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H2">
-        <v>22558</v>
+        <v>13638</v>
       </c>
       <c r="I2">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="J2">
-        <v>29.37</v>
+        <v>27.76</v>
       </c>
       <c r="K2">
-        <v>30.01</v>
+        <v>28.58</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>29.94</v>
+        <v>28.48</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>433</v>
+        <v>401</v>
       </c>
       <c r="D2">
-        <v>24.73</v>
+        <v>24.2</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H2">
-        <v>22367</v>
+        <v>13480</v>
       </c>
       <c r="I2">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="J2">
-        <v>29.62</v>
+        <v>28.07</v>
       </c>
       <c r="K2">
-        <v>30.27</v>
+        <v>28.89</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Adjusted.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>28.17</v>
+        <v>23.5</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -423,28 +423,28 @@
         <v>401</v>
       </c>
       <c r="D2">
-        <v>24.25</v>
+        <v>23.59</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H2">
-        <v>13638</v>
+        <v>13627</v>
       </c>
       <c r="I2">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
-        <v>27.76</v>
+        <v>23.11</v>
       </c>
       <c r="K2">
-        <v>28.58</v>
+        <v>23.9</v>
       </c>
     </row>
   </sheetData>
@@ -516,7 +516,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>28.48</v>
+        <v>24.34</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -525,28 +525,28 @@
         <v>401</v>
       </c>
       <c r="D2">
-        <v>24.2</v>
+        <v>23.58</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H2">
-        <v>13480</v>
+        <v>13159</v>
       </c>
       <c r="I2">
         <v>0.21</v>
       </c>
       <c r="J2">
-        <v>28.07</v>
+        <v>23.94</v>
       </c>
       <c r="K2">
-        <v>28.89</v>
+        <v>24.74</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Adjusted.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23.5</v>
+        <v>27.58</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -423,28 +423,28 @@
         <v>401</v>
       </c>
       <c r="D2">
-        <v>23.59</v>
+        <v>24.34</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H2">
-        <v>13627</v>
+        <v>15088</v>
       </c>
       <c r="I2">
         <v>0.2</v>
       </c>
       <c r="J2">
-        <v>23.11</v>
+        <v>27.19</v>
       </c>
       <c r="K2">
-        <v>23.9</v>
+        <v>27.96</v>
       </c>
     </row>
   </sheetData>
@@ -516,7 +516,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>24.34</v>
+        <v>27.89</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -525,28 +525,28 @@
         <v>401</v>
       </c>
       <c r="D2">
-        <v>23.58</v>
+        <v>24.3</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H2">
-        <v>13159</v>
+        <v>14915</v>
       </c>
       <c r="I2">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
-        <v>23.94</v>
+        <v>27.5</v>
       </c>
       <c r="K2">
-        <v>24.74</v>
+        <v>28.28</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Adjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>27.58</v>
+        <v>60.66</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>401</v>
+        <v>1422</v>
       </c>
       <c r="D2">
-        <v>24.34</v>
+        <v>53.6</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="H2">
-        <v>15088</v>
+        <v>15040</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="J2">
-        <v>27.19</v>
+        <v>59.8</v>
       </c>
       <c r="K2">
-        <v>27.96</v>
+        <v>61.51</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>27.89</v>
+        <v>38.29</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>401</v>
+        <v>671</v>
       </c>
       <c r="D2">
-        <v>24.3</v>
+        <v>36.12</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H2">
-        <v>14915</v>
+        <v>14934</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J2">
-        <v>27.5</v>
+        <v>37.71</v>
       </c>
       <c r="K2">
-        <v>28.28</v>
+        <v>38.87</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw-Adjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>60.66</v>
+        <v>27.58</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1422</v>
+        <v>401</v>
       </c>
       <c r="D2">
-        <v>53.6</v>
+        <v>24.34</v>
       </c>
       <c r="E2">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="H2">
-        <v>15040</v>
+        <v>15088</v>
       </c>
       <c r="I2">
-        <v>0.44</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
-        <v>59.8</v>
+        <v>27.19</v>
       </c>
       <c r="K2">
-        <v>61.51</v>
+        <v>27.96</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>38.29</v>
+        <v>27.89</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>671</v>
+        <v>401</v>
       </c>
       <c r="D2">
-        <v>36.12</v>
+        <v>24.3</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H2">
-        <v>14934</v>
+        <v>14915</v>
       </c>
       <c r="I2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
-        <v>37.71</v>
+        <v>27.5</v>
       </c>
       <c r="K2">
-        <v>38.87</v>
+        <v>28.28</v>
       </c>
     </row>
   </sheetData>
